--- a/Data/subjects_COMPS.xlsx
+++ b/Data/subjects_COMPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4769AA-8846-436B-BAC4-ED8CA0ABE137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAFADCE-E572-47D2-97FD-56C07ACBE8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subjects Template" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>Subject Name</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>CEDLL7038</t>
+  </si>
+  <si>
+    <t>Elective</t>
   </si>
 </sst>
 </file>
@@ -400,12 +403,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,14 +713,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.77734375" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,8 +733,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E1" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
@@ -743,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -757,7 +765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -771,7 +779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -785,7 +793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -799,21 +807,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -827,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -841,7 +849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -855,7 +863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -869,7 +877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -883,7 +891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -897,7 +905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -910,8 +918,11 @@
       <c r="D14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -924,8 +935,11 @@
       <c r="D15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="D16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -952,8 +969,11 @@
       <c r="D17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -966,12 +986,15 @@
       <c r="D18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -981,7 +1004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -995,7 +1018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1009,7 +1032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1022,8 +1045,11 @@
       <c r="D22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1036,8 +1062,11 @@
       <c r="D23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1050,8 +1079,11 @@
       <c r="D24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -1064,8 +1096,11 @@
       <c r="D25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1078,8 +1113,11 @@
       <c r="D26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1093,7 +1131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -1107,7 +1145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -1120,8 +1158,11 @@
       <c r="D29">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -1134,8 +1175,11 @@
       <c r="D30">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -1148,8 +1192,11 @@
       <c r="D31">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -1162,8 +1209,11 @@
       <c r="D32">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1177,7 +1227,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -1191,7 +1241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -1204,8 +1254,11 @@
       <c r="D35">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1218,8 +1271,11 @@
       <c r="D36">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1232,8 +1288,11 @@
       <c r="D37">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1245,6 +1304,9 @@
       </c>
       <c r="D38">
         <v>7</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1256,64 +1318,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
